--- a/output/pdf_financials_xlsx/CEN.H.xlsx
+++ b/output/pdf_financials_xlsx/CEN.H.xlsx
@@ -5809,28 +5809,28 @@
         <v>8.001087999999999</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>8.001087999999999</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>8.001087999999999</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>8.001087999999999</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>8.001087999999999</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>8.001087999999999</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>8.001087999999999</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>8.001087999999999</v>
       </c>
     </row>
     <row r="93">
@@ -7252,16 +7252,16 @@
         <v>-0.200307</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.012981</v>
+        <v>-2.838994</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.101528</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.115038</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.04659</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>0</v>
@@ -9316,7 +9316,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -12064,7 +12068,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -13578,7 +13586,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -22844,7 +22856,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CEN.H.xlsx
+++ b/output/pdf_financials_xlsx/CEN.H.xlsx
@@ -1039,19 +1039,19 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.029183</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.147356</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.007011</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000513</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>4.5e-05</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -2038,19 +2038,19 @@
         <v>-0.424554</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.699223</v>
+        <v>-0.728406</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.511925</v>
+        <v>-5.659281</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.170171</v>
+        <v>-2.177182</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.392627</v>
+        <v>-1.39314</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.118808</v>
+        <v>-3.118853</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-4.494194</v>
@@ -2156,19 +2156,19 @@
         <v>-0.424554</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.699223</v>
+        <v>-0.728406</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.500001</v>
+        <v>-5.647357</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.160439</v>
+        <v>-2.16745</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.385815</v>
+        <v>-1.386328</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.111996</v>
+        <v>-3.112041</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-4.490856</v>
@@ -2447,52 +2447,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.003377</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.4282</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.181307</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.656589</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.104628</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.409469</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.822205</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.410803</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.095751</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.022931</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.089493</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.247778</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.122597</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.052593</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.001857</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.031593</v>
       </c>
     </row>
     <row r="35">
@@ -2557,52 +2557,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.003377</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.4282</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.181307</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.656589</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.104628</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.409469</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.822205</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.410803</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.095751</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.022931</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.089493</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.247778</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.122597</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.052593</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.001857</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.031593</v>
       </c>
     </row>
     <row r="37">
@@ -3217,52 +3217,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.027365</v>
+        <v>0.023988</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.43579</v>
+        <v>0.00759</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>9.076421</v>
+        <v>4.895114</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.275619</v>
+        <v>1.61903</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.16753</v>
+        <v>0.062902</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.426518</v>
+        <v>0.017049</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.83891</v>
+        <v>0.016705</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.426153</v>
+        <v>0.01535</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.108344</v>
+        <v>0.012593</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.035351</v>
+        <v>0.01242</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.100312</v>
+        <v>0.010819</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.252089</v>
+        <v>0.004311</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.132505</v>
+        <v>0.009908</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.060713</v>
+        <v>0.00812</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.00269</v>
+        <v>0.000833</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.032893</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="49">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
@@ -31984,7 +31984,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -33120,7 +33120,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -34026,7 +34026,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -35214,7 +35214,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -35954,7 +35954,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -37646,7 +37646,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">

--- a/output/pdf_financials_xlsx/CEN.H.xlsx
+++ b/output/pdf_financials_xlsx/CEN.H.xlsx
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>16.211526</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>17.682546</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>23.013555</v>
@@ -17674,7 +17674,11 @@
           <t>Share capital - note 7</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="n">
         <v>16.211526</v>
       </c>
@@ -18342,7 +18346,11 @@
           <t>Share capital - note 7</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E107" s="5" t="n">
         <v>16.211526</v>
       </c>
